--- a/src/scraping/data/argos_test.xlsx.xlsx
+++ b/src/scraping/data/argos_test.xlsx.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA8A557-A77C-4EB9-B4B4-60AD5D7B90BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2928" yWindow="2928" windowWidth="14070" windowHeight="8472" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
